--- a/StructureDefinition-openimis-location.xlsx
+++ b/StructureDefinition-openimis-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9689,7 +9689,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>22</v>
@@ -9909,7 +9909,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>22</v>
@@ -10022,7 +10022,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>22</v>
@@ -10246,7 +10246,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>22</v>
@@ -10468,7 +10468,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>22</v>
@@ -10690,7 +10690,7 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>22</v>
@@ -11463,7 +11463,7 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>22</v>
@@ -11798,7 +11798,7 @@
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>22</v>
@@ -12020,7 +12020,7 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-location.xlsx
+++ b/StructureDefinition-openimis-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-location.xlsx
+++ b/StructureDefinition-openimis-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
